--- a/public/journal_template.xlsx
+++ b/public/journal_template.xlsx
@@ -8163,59 +8163,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A2:G576" totalsRowShown="0" tableBorderDxfId="13">
-  <tableColumns count="7">
-    <tableColumn id="1" name="Month" dataDxfId="12"/>
-    <tableColumn id="2" name="Date" dataDxfId="11"/>
-    <tableColumn id="3" name="Narration (Reason)" dataDxfId="10"/>
-    <tableColumn id="4" name="Account code" dataDxfId="9">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(E3,Accounts!$B$2:$C$66,2,FALSE),0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" name="Account name " dataDxfId="8"/>
-    <tableColumn id="6" name="Debit" dataDxfId="7" dataCellStyle="Comma"/>
-    <tableColumn id="7" name="Credit" dataDxfId="6" dataCellStyle="Comma"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:G68" totalsRowShown="0">
-  <autoFilter ref="A3:G68"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Month" dataDxfId="5"/>
-    <tableColumn id="2" name="Date" dataDxfId="4"/>
-    <tableColumn id="3" name="Narration (Reason)"/>
-    <tableColumn id="4" name="Account code"/>
-    <tableColumn id="5" name="Account name "/>
-    <tableColumn id="6" name="Debit"/>
-    <tableColumn id="7" name="Credit"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H18" totalsRowShown="0">
-  <autoFilter ref="A1:H18"/>
-  <sortState ref="A2:G34">
-    <sortCondition ref="A2:A34"/>
-  </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Month" dataDxfId="3"/>
-    <tableColumn id="2" name="Date" dataDxfId="2"/>
-    <tableColumn id="3" name="Narration (Reason)"/>
-    <tableColumn id="4" name="Account code"/>
-    <tableColumn id="5" name="Account name "/>
-    <tableColumn id="6" name="Debit"/>
-    <tableColumn id="7" name="Credit"/>
-    <tableColumn id="8" name="Column1"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -21235,9 +21182,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -23769,9 +23713,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -24475,9 +24416,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
